--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.66880049705937</v>
+        <v>4.008680080772148</v>
       </c>
       <c r="D2" t="n">
-        <v>21.21653475929945</v>
+        <v>3.447686898386161</v>
       </c>
       <c r="E2" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F2" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.36341613681874</v>
+        <v>8.834055122233046</v>
       </c>
       <c r="D3" t="n">
-        <v>54.23979593065074</v>
+        <v>8.813966838730744</v>
       </c>
       <c r="E3" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F3" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.15927716062027</v>
+        <v>2.625882538600794</v>
       </c>
       <c r="D4" t="n">
-        <v>16.08041745652494</v>
+        <v>2.613067836685302</v>
       </c>
       <c r="E4" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F4" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>2.947485899914351</v>
+        <v>0.4789664587360821</v>
       </c>
       <c r="D5" t="n">
-        <v>16.86034306452584</v>
+        <v>2.739805747985449</v>
       </c>
       <c r="E5" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F5" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.29760255899752</v>
+        <v>0.698360415837097</v>
       </c>
       <c r="D6" t="n">
-        <v>7.117073230481433</v>
+        <v>1.156524399953233</v>
       </c>
       <c r="E6" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F6" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.18465843842649</v>
+        <v>1.005006996244305</v>
       </c>
       <c r="D7" t="n">
-        <v>13.15394039660003</v>
+        <v>2.137515314447505</v>
       </c>
       <c r="E7" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F7" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.103047896826602</v>
+        <v>0.5042452832343229</v>
       </c>
       <c r="D8" t="n">
-        <v>13.58920951665339</v>
+        <v>2.208246546456175</v>
       </c>
       <c r="E8" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F8" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.49095372999023</v>
+        <v>4.629779981123414</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17865361123402</v>
+        <v>4.904031211825528</v>
       </c>
       <c r="E9" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F9" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.68594659920328</v>
+        <v>2.711466322370533</v>
       </c>
       <c r="D10" t="n">
-        <v>9.496263592709614</v>
+        <v>1.543142833815312</v>
       </c>
       <c r="E10" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F10" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.4639724664927</v>
+        <v>2.512895525805065</v>
       </c>
       <c r="D11" t="n">
-        <v>18.21665095131611</v>
+        <v>2.960205779588868</v>
       </c>
       <c r="E11" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F11" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.481830658533097</v>
+        <v>1.378297482011628</v>
       </c>
       <c r="D12" t="n">
-        <v>8.301606447105216</v>
+        <v>1.349011047654598</v>
       </c>
       <c r="E12" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F12" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.314718542707531</v>
+        <v>1.351141763189974</v>
       </c>
       <c r="D13" t="n">
-        <v>8.998849422548709</v>
+        <v>1.462313031164165</v>
       </c>
       <c r="E13" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F13" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>2.463591147981695</v>
+        <v>0.4003335615470254</v>
       </c>
       <c r="D14" t="n">
-        <v>2.931999064981185</v>
+        <v>0.4764498480594426</v>
       </c>
       <c r="E14" t="n">
-        <v>14.01067949859085</v>
+        <v>2.276735418521013</v>
       </c>
       <c r="F14" t="n">
-        <v>12.70544247484283</v>
+        <v>2.06463440216196</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
